--- a/Data Files/write.xlsx
+++ b/Data Files/write.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17433" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18543" uniqueCount="88">
   <si>
     <t>role_type</t>
   </si>
